--- a/stories/arbres/TREE-JEU-033.xlsx
+++ b/stories/arbres/TREE-JEU-033.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde est au parc avec papa. Papa dit une règle. La règle : on attend. Puis on joue. Papa va rappeler la règle une fois. Clotilde écoute. Une règle. La rappeler.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac, la marelle, ou le cerceau.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, papa dit une règle. Clotilde écoute. Papa va rappeler la règle. Clotilde la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, que suit Clotilde ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde a suivi une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2229,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre attendre, passer, ou s'arrêter.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2396,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2537,6 +2589,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2701,6 +2758,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Léa à le bac. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2925,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3092,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Tom à le bac. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3259,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3426,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Sami à le bac. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3861,6 +3953,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4025,6 +4122,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Léa à le bac. Elle a su passer. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4289,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4456,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Tom à le bac. Elle a su passer. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4623,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4673,6 +4790,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Sami à le bac. Elle a su passer. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4957,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4997,6 +5124,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5185,6 +5317,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5349,6 +5486,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Léa à le bac. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5653,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5820,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Tom à le bac. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5987,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6154,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Sami à le bac. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6321,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6321,6 +6488,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À la marelle, une règle. Papa la rappelle. Clotilde attend. Puis elle saute.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6501,6 +6673,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À la marelle, que suit Clotilde ?</t>
         </is>
       </c>
     </row>
@@ -6669,6 +6846,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Une règle. L'adulte la rappelle.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6859,6 +7041,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre attendre, passer, ou s'arrêter.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7021,6 +7208,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7209,6 +7401,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7373,6 +7570,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Léa à la marelle. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7535,6 +7737,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7697,6 +7904,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Tom à la marelle. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7859,6 +8071,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8021,6 +8238,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Sami à la marelle. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8183,6 +8405,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8345,6 +8572,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8533,6 +8765,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8697,6 +8934,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Léa à la marelle. Elle a su passer. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8859,6 +9101,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9021,6 +9268,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Tom à la marelle. Elle a su passer. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9183,6 +9435,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9345,6 +9602,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Sami à la marelle. Elle a su passer. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9507,6 +9769,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9669,6 +9936,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9857,6 +10129,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10021,6 +10298,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Léa à la marelle. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10183,6 +10465,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10345,6 +10632,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Tom à la marelle. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10507,6 +10799,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10669,6 +10966,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Sami à la marelle. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10831,6 +11133,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10993,6 +11300,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Au cerceau, une règle. Papa la rappelle. Clotilde attend. Puis elle passe.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11169,6 +11481,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Au cerceau, que suit Clotilde ?</t>
         </is>
       </c>
     </row>
@@ -11337,6 +11654,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde a écouté la règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11527,6 +11849,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre attendre, passer, ou s'arrêter.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11689,6 +12016,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11877,6 +12209,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12041,6 +12378,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Léa à le cerceau. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12203,6 +12545,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12365,6 +12712,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Tom à le cerceau. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12527,6 +12879,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12689,6 +13046,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Sami à le cerceau. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12851,6 +13213,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13013,6 +13380,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13201,6 +13573,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13365,6 +13742,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Léa à le cerceau. Elle a su passer. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13527,6 +13909,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13689,6 +14076,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Tom à le cerceau. Elle a su passer. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13851,6 +14243,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14013,6 +14410,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Sami à le cerceau. Elle a su passer. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14175,6 +14577,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14337,6 +14744,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14525,6 +14937,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14689,6 +15106,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Léa à le cerceau. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14851,6 +15273,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15013,6 +15440,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Tom à le cerceau. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15175,6 +15607,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15337,6 +15774,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Clotilde rejoint Sami à le cerceau. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15499,6 +15941,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15517,7 +15964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15590,6 +16037,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-JEU-033.xlsx
+++ b/stories/arbres/TREE-JEU-033.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|Clotilde est au parc avec papa. Papa dit une règle. La règle : on attend. Puis on joue. Papa va rappeler la règle une fois. Clotilde écoute. Une règle. La rappeler.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1528,7 @@
           <t>narrateur|On peut prendre le bac, la marelle, ou le cerceau.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1696,7 @@
           <t>narrateur|Au bac, papa dit une règle. Clotilde écoute. Papa va rappeler la règle. Clotilde la suit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1880,7 @@
           <t>narrateur|Au bac, que suit Clotilde ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2052,7 @@
           <t>narrateur|Clotilde a suivi une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2248,7 @@
           <t>narrateur|On peut prendre attendre, passer, ou s'arrêter.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2416,7 @@
           <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2596,6 +2612,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2763,6 +2780,7 @@
           <t>narrateur|Clotilde rejoint Léa à le bac. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2930,6 +2948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3097,6 +3116,7 @@
           <t>narrateur|Clotilde rejoint Tom à le bac. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3264,6 +3284,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3452,7 @@
           <t>narrateur|Clotilde rejoint Sami à le bac. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3620,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3788,7 @@
           <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3960,6 +3984,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4127,6 +4152,7 @@
           <t>narrateur|Clotilde rejoint Léa à le bac. Elle a su passer. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4294,6 +4320,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4461,6 +4488,7 @@
           <t>narrateur|Clotilde rejoint Tom à le bac. Elle a su passer. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4628,6 +4656,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4795,6 +4824,7 @@
           <t>narrateur|Clotilde rejoint Sami à le bac. Elle a su passer. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4962,6 +4992,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5129,6 +5160,7 @@
           <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5324,6 +5356,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5491,6 +5524,7 @@
           <t>narrateur|Clotilde rejoint Léa à le bac. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5658,6 +5692,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5825,6 +5860,7 @@
           <t>narrateur|Clotilde rejoint Tom à le bac. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5992,6 +6028,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6159,6 +6196,7 @@
           <t>narrateur|Clotilde rejoint Sami à le bac. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6326,6 +6364,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6493,6 +6532,7 @@
           <t>narrateur|À la marelle, une règle. Papa la rappelle. Clotilde attend. Puis elle saute.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6680,6 +6720,7 @@
           <t>narrateur|À la marelle, que suit Clotilde ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6851,6 +6892,7 @@
           <t>narrateur|Oui. Une règle. L'adulte la rappelle.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7046,6 +7088,7 @@
           <t>narrateur|On peut prendre attendre, passer, ou s'arrêter.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7213,6 +7256,7 @@
           <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7408,6 +7452,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7575,6 +7620,7 @@
           <t>narrateur|Clotilde rejoint Léa à la marelle. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7742,6 +7788,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7909,6 +7956,7 @@
           <t>narrateur|Clotilde rejoint Tom à la marelle. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8076,6 +8124,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8243,6 +8292,7 @@
           <t>narrateur|Clotilde rejoint Sami à la marelle. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8410,6 +8460,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8577,6 +8628,7 @@
           <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8772,6 +8824,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8939,6 +8992,7 @@
           <t>narrateur|Clotilde rejoint Léa à la marelle. Elle a su passer. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9106,6 +9160,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9273,6 +9328,7 @@
           <t>narrateur|Clotilde rejoint Tom à la marelle. Elle a su passer. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9440,6 +9496,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9607,6 +9664,7 @@
           <t>narrateur|Clotilde rejoint Sami à la marelle. Elle a su passer. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9774,6 +9832,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9941,6 +10000,7 @@
           <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10136,6 +10196,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10303,6 +10364,7 @@
           <t>narrateur|Clotilde rejoint Léa à la marelle. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10470,6 +10532,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10637,6 +10700,7 @@
           <t>narrateur|Clotilde rejoint Tom à la marelle. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10804,6 +10868,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10971,6 +11036,7 @@
           <t>narrateur|Clotilde rejoint Sami à la marelle. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11138,6 +11204,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11305,6 +11372,7 @@
           <t>narrateur|Au cerceau, une règle. Papa la rappelle. Clotilde attend. Puis elle passe.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11488,6 +11556,7 @@
           <t>narrateur|Au cerceau, que suit Clotilde ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11659,6 +11728,7 @@
           <t>narrateur|Clotilde a écouté la règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11854,6 +11924,7 @@
           <t>narrateur|On peut prendre attendre, passer, ou s'arrêter.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12021,6 +12092,7 @@
           <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12216,6 +12288,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12383,6 +12456,7 @@
           <t>narrateur|Clotilde rejoint Léa à le cerceau. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12550,6 +12624,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12717,6 +12792,7 @@
           <t>narrateur|Clotilde rejoint Tom à le cerceau. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12884,6 +12960,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13051,6 +13128,7 @@
           <t>narrateur|Clotilde rejoint Sami à le cerceau. Elle a su attendre. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13218,6 +13296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13385,6 +13464,7 @@
           <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13580,6 +13660,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13747,6 +13828,7 @@
           <t>narrateur|Clotilde rejoint Léa à le cerceau. Elle a su passer. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13914,6 +13996,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14081,6 +14164,7 @@
           <t>narrateur|Clotilde rejoint Tom à le cerceau. Elle a su passer. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14248,6 +14332,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14415,6 +14500,7 @@
           <t>narrateur|Clotilde rejoint Sami à le cerceau. Elle a su passer. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14582,6 +14668,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14749,6 +14836,7 @@
           <t>narrateur|Une règle. Papa la rappelle. Clotilde la suit.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14944,6 +15032,7 @@
           <t>narrateur|On peut prendre Léa, Tom, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15111,6 +15200,7 @@
           <t>narrateur|Clotilde rejoint Léa à le cerceau. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15278,6 +15368,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15445,6 +15536,7 @@
           <t>narrateur|Clotilde rejoint Tom à le cerceau. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15612,6 +15704,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15779,6 +15872,7 @@
           <t>narrateur|Clotilde rejoint Sami à le cerceau. Elle a su s'arrêter. Une règle. Papa l'a rappelée.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15946,6 +16040,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15964,7 +16059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16044,6 +16139,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16245,6 +16354,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
